--- a/九龙-旺角-映居/映居_销控明细表.xlsx
+++ b/九龙-旺角-映居/映居_销控明细表.xlsx
@@ -1007,34 +1007,34 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>9762900</v>
+        <v>8591300</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>28298</v>
+        <v>24902</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>8591352</v>
+        <v>8591300</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>24902</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8446,12 +8446,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
-$976万
-$28,298/呎
-(在售)</t>
+$859万
+$24,902/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">

--- a/九龙-旺角-映居/映居_销控明细表.xlsx
+++ b/九龙-旺角-映居/映居_销控明细表.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>建築期付款</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">

--- a/九龙-旺角-映居/映居_销控明细表.xlsx
+++ b/九龙-旺角-映居/映居_销控明细表.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -8451,7 +8451,7 @@
           <t>B | 345呎 (1房)
 $859万
 $24,902/呎
-(26年-09月-12日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">

--- a/九龙-旺角-映居/映居_销控明细表.xlsx
+++ b/九龙-旺角-映居/映居_销控明细表.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
